--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/NEW_YORK_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/NEW_YORK_2014.xlsx
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C93">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C234">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C243">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C701">
@@ -13902,7 +13902,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C753">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C763">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C871">
@@ -22110,7 +22110,7 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1209">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1256">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1397">
